--- a/Data/EXCEL/Transfer/salemon/202208/8423-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8423-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB20EBE2-5BD2-4952-9FF6-E75E32425621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9397BBD1-CB7E-4EF8-8E4A-695BB51DFC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8423-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -72,12 +72,15 @@
   <si>
     <t>年增</t>
   </si>
+  <si>
+    <t>-</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -243,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -260,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -268,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -815,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -824,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -842,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1215,20 +1226,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q63"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:Q144"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="5" width="10.125" customWidth="1"/>
-    <col min="6" max="6" width="9.5" customWidth="1"/>
-    <col min="7" max="7" width="11.125" customWidth="1"/>
-    <col min="8" max="11" width="10.125" customWidth="1"/>
-    <col min="12" max="12" width="9.5" customWidth="1"/>
-    <col min="13" max="16" width="10.125" customWidth="1"/>
-    <col min="17" max="17" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="2" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="13.375" customWidth="1"/>
+    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="8" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="12" width="13.375" customWidth="1"/>
+    <col min="13" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1255,7 +1266,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1294,7 +1305,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1337,7 +1348,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1376,7 +1387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1429,7 +1440,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1482,7 +1493,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1535,7 +1546,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1588,7 +1599,7 @@
         <v>-9.27</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1641,7 +1652,7 @@
         <v>-12.8</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1694,7 +1705,7 @@
         <v>-10.4</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1747,7 +1758,7 @@
         <v>-12.7</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1800,7 +1811,7 @@
         <v>-8.5299999999999994</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1853,7 +1864,7 @@
         <v>-4.47</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1906,7 +1917,7 @@
         <v>-2.4500000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1959,7 +1970,7 @@
         <v>-3.92</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2012,7 +2023,7 @@
         <v>-3.43</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2065,7 +2076,7 @@
         <v>-2.04</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2118,7 +2129,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2171,7 +2182,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2224,7 +2235,7 @@
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2277,7 +2288,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2330,7 +2341,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2383,7 +2394,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2436,7 +2447,7 @@
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2489,7 +2500,7 @@
         <v>-14.5</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2542,7 +2553,7 @@
         <v>-17.8</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2595,7 +2606,7 @@
         <v>-17.3</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2648,7 +2659,7 @@
         <v>-18.7</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2701,7 +2712,7 @@
         <v>-21.3</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2754,7 +2765,7 @@
         <v>-22.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2807,7 +2818,7 @@
         <v>-24.8</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2860,7 +2871,7 @@
         <v>-28.5</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2913,7 +2924,7 @@
         <v>-23.9</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2966,7 +2977,7 @@
         <v>-16.2</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3019,7 +3030,7 @@
         <v>-9.9700000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3072,7 +3083,7 @@
         <v>-27.9</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3125,7 +3136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3178,7 +3189,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3231,7 +3242,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3284,7 +3295,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3337,7 +3348,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3390,7 +3401,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3443,7 +3454,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3496,7 +3507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3549,7 +3560,7 @@
         <v>-0.68</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3602,7 +3613,7 @@
         <v>-7.97</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3655,7 +3666,7 @@
         <v>-3.8</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3708,7 +3719,7 @@
         <v>-3.23</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3761,7 +3772,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3814,7 +3825,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3867,7 +3878,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3920,7 +3931,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3973,7 +3984,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4026,7 +4037,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4079,7 +4090,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4132,7 +4143,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4185,7 +4196,7 @@
         <v>33.700000000000003</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4238,7 +4249,7 @@
         <v>40.9</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4291,7 +4302,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4344,7 +4355,7 @@
         <v>84.3</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4397,7 +4408,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4450,7 +4461,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4501,6 +4512,4299 @@
       </c>
       <c r="Q63" s="8">
         <v>23.9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>42979</v>
+      </c>
+      <c r="B64" s="7">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="C64" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="D64" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="E64" s="7">
+        <v>19</v>
+      </c>
+      <c r="F64" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="G64" s="8">
+        <v>3.02</v>
+      </c>
+      <c r="H64" s="9">
+        <v>0.246</v>
+      </c>
+      <c r="I64" s="10">
+        <v>-1.95</v>
+      </c>
+      <c r="J64" s="8">
+        <v>62.3</v>
+      </c>
+      <c r="K64" s="9">
+        <v>2.09</v>
+      </c>
+      <c r="L64" s="8">
+        <v>23.3</v>
+      </c>
+      <c r="M64" s="9">
+        <v>0.246</v>
+      </c>
+      <c r="N64" s="10">
+        <v>-1.95</v>
+      </c>
+      <c r="O64" s="8">
+        <v>62.3</v>
+      </c>
+      <c r="P64" s="9">
+        <v>2.09</v>
+      </c>
+      <c r="Q64" s="8">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>42948</v>
+      </c>
+      <c r="B65" s="7">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="C65" s="7">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="D65" s="7">
+        <v>22.85</v>
+      </c>
+      <c r="E65" s="7">
+        <v>18.55</v>
+      </c>
+      <c r="F65" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="G65" s="8">
+        <v>8.15</v>
+      </c>
+      <c r="H65" s="9">
+        <v>0.251</v>
+      </c>
+      <c r="I65" s="10">
+        <v>-2.63</v>
+      </c>
+      <c r="J65" s="8">
+        <v>39</v>
+      </c>
+      <c r="K65" s="9">
+        <v>1.85</v>
+      </c>
+      <c r="L65" s="8">
+        <v>19.5</v>
+      </c>
+      <c r="M65" s="9">
+        <v>0.251</v>
+      </c>
+      <c r="N65" s="10">
+        <v>-2.63</v>
+      </c>
+      <c r="O65" s="8">
+        <v>39</v>
+      </c>
+      <c r="P65" s="9">
+        <v>1.85</v>
+      </c>
+      <c r="Q65" s="8">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>42917</v>
+      </c>
+      <c r="B66" s="7">
+        <v>18.05</v>
+      </c>
+      <c r="C66" s="7">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D66" s="7">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="E66" s="7">
+        <v>17.8</v>
+      </c>
+      <c r="F66" s="10">
+        <v>-0.05</v>
+      </c>
+      <c r="G66" s="10">
+        <v>-0.27</v>
+      </c>
+      <c r="H66" s="9">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="I66" s="8">
+        <v>2.06</v>
+      </c>
+      <c r="J66" s="8">
+        <v>50.9</v>
+      </c>
+      <c r="K66" s="9">
+        <v>1.59</v>
+      </c>
+      <c r="L66" s="8">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="M66" s="9">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="N66" s="8">
+        <v>2.06</v>
+      </c>
+      <c r="O66" s="8">
+        <v>50.9</v>
+      </c>
+      <c r="P66" s="9">
+        <v>1.59</v>
+      </c>
+      <c r="Q66" s="8">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>42887</v>
+      </c>
+      <c r="B67" s="7">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="C67" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="D67" s="7">
+        <v>19</v>
+      </c>
+      <c r="E67" s="7">
+        <v>17.5</v>
+      </c>
+      <c r="F67" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="G67" s="8">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="H67" s="9">
+        <v>0.253</v>
+      </c>
+      <c r="I67" s="10">
+        <v>-3.46</v>
+      </c>
+      <c r="J67" s="8">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="K67" s="9">
+        <v>1.34</v>
+      </c>
+      <c r="L67" s="8">
+        <v>12</v>
+      </c>
+      <c r="M67" s="9">
+        <v>0.253</v>
+      </c>
+      <c r="N67" s="10">
+        <v>-3.46</v>
+      </c>
+      <c r="O67" s="8">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="P67" s="9">
+        <v>1.34</v>
+      </c>
+      <c r="Q67" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>42856</v>
+      </c>
+      <c r="B68" s="7">
+        <v>17.95</v>
+      </c>
+      <c r="C68" s="7">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D68" s="7">
+        <v>18.850000000000001</v>
+      </c>
+      <c r="E68" s="7">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="F68" s="10">
+        <v>-0.45</v>
+      </c>
+      <c r="G68" s="10">
+        <v>-2.4900000000000002</v>
+      </c>
+      <c r="H68" s="9">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="I68" s="8">
+        <v>25</v>
+      </c>
+      <c r="J68" s="8">
+        <v>16.3</v>
+      </c>
+      <c r="K68" s="9">
+        <v>1.08</v>
+      </c>
+      <c r="L68" s="8">
+        <v>6.99</v>
+      </c>
+      <c r="M68" s="9">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="N68" s="8">
+        <v>25</v>
+      </c>
+      <c r="O68" s="8">
+        <v>16.3</v>
+      </c>
+      <c r="P68" s="9">
+        <v>1.08</v>
+      </c>
+      <c r="Q68" s="8">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>42826</v>
+      </c>
+      <c r="B69" s="7">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="C69" s="7">
+        <v>18.05</v>
+      </c>
+      <c r="D69" s="7">
+        <v>20.149999999999999</v>
+      </c>
+      <c r="E69" s="7">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="F69" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="G69" s="8">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H69" s="9">
+        <v>0.21</v>
+      </c>
+      <c r="I69" s="10">
+        <v>-18.100000000000001</v>
+      </c>
+      <c r="J69" s="10">
+        <v>-4.26</v>
+      </c>
+      <c r="K69" s="9">
+        <v>0.82199999999999995</v>
+      </c>
+      <c r="L69" s="8">
+        <v>4.32</v>
+      </c>
+      <c r="M69" s="9">
+        <v>0.21</v>
+      </c>
+      <c r="N69" s="10">
+        <v>-18.100000000000001</v>
+      </c>
+      <c r="O69" s="10">
+        <v>-4.26</v>
+      </c>
+      <c r="P69" s="9">
+        <v>0.82199999999999995</v>
+      </c>
+      <c r="Q69" s="8">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>42795</v>
+      </c>
+      <c r="B70" s="7">
+        <v>17.649999999999999</v>
+      </c>
+      <c r="C70" s="7">
+        <v>18</v>
+      </c>
+      <c r="D70" s="7">
+        <v>19</v>
+      </c>
+      <c r="E70" s="7">
+        <v>17</v>
+      </c>
+      <c r="F70" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="G70" s="8">
+        <v>1.98</v>
+      </c>
+      <c r="H70" s="9">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="I70" s="8">
+        <v>36.1</v>
+      </c>
+      <c r="J70" s="8">
+        <v>34.4</v>
+      </c>
+      <c r="K70" s="9">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="L70" s="8">
+        <v>7.62</v>
+      </c>
+      <c r="M70" s="9">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="N70" s="8">
+        <v>36.1</v>
+      </c>
+      <c r="O70" s="8">
+        <v>34.4</v>
+      </c>
+      <c r="P70" s="9">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="Q70" s="8">
+        <v>7.62</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>42767</v>
+      </c>
+      <c r="B71" s="7">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="C71" s="7">
+        <v>17.649999999999999</v>
+      </c>
+      <c r="D71" s="7">
+        <v>18.8</v>
+      </c>
+      <c r="E71" s="7">
+        <v>17.45</v>
+      </c>
+      <c r="F71" s="10">
+        <v>-0.9</v>
+      </c>
+      <c r="G71" s="10">
+        <v>-4.8499999999999996</v>
+      </c>
+      <c r="H71" s="9">
+        <v>0.188</v>
+      </c>
+      <c r="I71" s="8">
+        <v>11.9</v>
+      </c>
+      <c r="J71" s="8">
+        <v>3.22</v>
+      </c>
+      <c r="K71" s="9">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="L71" s="10">
+        <v>-5.85</v>
+      </c>
+      <c r="M71" s="9">
+        <v>0.188</v>
+      </c>
+      <c r="N71" s="8">
+        <v>11.9</v>
+      </c>
+      <c r="O71" s="8">
+        <v>3.22</v>
+      </c>
+      <c r="P71" s="9">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="Q71" s="10">
+        <v>-5.85</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>42736</v>
+      </c>
+      <c r="B72" s="7">
+        <v>18.55</v>
+      </c>
+      <c r="C72" s="7">
+        <v>18.55</v>
+      </c>
+      <c r="D72" s="7">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="E72" s="7">
+        <v>18</v>
+      </c>
+      <c r="F72" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G72" s="8">
+        <v>3.06</v>
+      </c>
+      <c r="H72" s="9">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="I72" s="10">
+        <v>-10.6</v>
+      </c>
+      <c r="J72" s="10">
+        <v>-14.3</v>
+      </c>
+      <c r="K72" s="9">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="L72" s="10">
+        <v>-14.3</v>
+      </c>
+      <c r="M72" s="9">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="N72" s="10">
+        <v>-10.6</v>
+      </c>
+      <c r="O72" s="10">
+        <v>-14.3</v>
+      </c>
+      <c r="P72" s="9">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="Q72" s="10">
+        <v>-14.3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>42705</v>
+      </c>
+      <c r="B73" s="7">
+        <v>15.2</v>
+      </c>
+      <c r="C73" s="7">
+        <v>18</v>
+      </c>
+      <c r="D73" s="7">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="E73" s="7">
+        <v>15</v>
+      </c>
+      <c r="F73" s="8">
+        <v>3</v>
+      </c>
+      <c r="G73" s="8">
+        <v>20</v>
+      </c>
+      <c r="H73" s="9">
+        <v>0.188</v>
+      </c>
+      <c r="I73" s="10">
+        <v>-10.3</v>
+      </c>
+      <c r="J73" s="10">
+        <v>-15.2</v>
+      </c>
+      <c r="K73" s="9">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="L73" s="10">
+        <v>-19.5</v>
+      </c>
+      <c r="M73" s="9">
+        <v>0.188</v>
+      </c>
+      <c r="N73" s="10">
+        <v>-10.3</v>
+      </c>
+      <c r="O73" s="10">
+        <v>-15.2</v>
+      </c>
+      <c r="P73" s="9">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="Q73" s="10">
+        <v>-19.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>42675</v>
+      </c>
+      <c r="B74" s="7">
+        <v>16.3</v>
+      </c>
+      <c r="C74" s="7">
+        <v>15</v>
+      </c>
+      <c r="D74" s="7">
+        <v>16.350000000000001</v>
+      </c>
+      <c r="E74" s="7">
+        <v>14.85</v>
+      </c>
+      <c r="F74" s="10">
+        <v>-1.2</v>
+      </c>
+      <c r="G74" s="10">
+        <v>-7.41</v>
+      </c>
+      <c r="H74" s="9">
+        <v>0.21</v>
+      </c>
+      <c r="I74" s="8">
+        <v>10.9</v>
+      </c>
+      <c r="J74" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K74" s="9">
+        <v>2.1</v>
+      </c>
+      <c r="L74" s="10">
+        <v>-19.899999999999999</v>
+      </c>
+      <c r="M74" s="9">
+        <v>0.21</v>
+      </c>
+      <c r="N74" s="8">
+        <v>10.9</v>
+      </c>
+      <c r="O74" s="8">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="P74" s="9">
+        <v>2.1</v>
+      </c>
+      <c r="Q74" s="10">
+        <v>-19.899999999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>42644</v>
+      </c>
+      <c r="B75" s="7">
+        <v>17.95</v>
+      </c>
+      <c r="C75" s="7">
+        <v>16.2</v>
+      </c>
+      <c r="D75" s="7">
+        <v>17.95</v>
+      </c>
+      <c r="E75" s="7">
+        <v>16</v>
+      </c>
+      <c r="F75" s="10">
+        <v>-1.75</v>
+      </c>
+      <c r="G75" s="10">
+        <v>-9.75</v>
+      </c>
+      <c r="H75" s="9">
+        <v>0.189</v>
+      </c>
+      <c r="I75" s="8">
+        <v>24.6</v>
+      </c>
+      <c r="J75" s="10">
+        <v>-20.399999999999999</v>
+      </c>
+      <c r="K75" s="9">
+        <v>1.89</v>
+      </c>
+      <c r="L75" s="10">
+        <v>-21.7</v>
+      </c>
+      <c r="M75" s="9">
+        <v>0.189</v>
+      </c>
+      <c r="N75" s="8">
+        <v>24.6</v>
+      </c>
+      <c r="O75" s="10">
+        <v>-20.399999999999999</v>
+      </c>
+      <c r="P75" s="9">
+        <v>1.89</v>
+      </c>
+      <c r="Q75" s="10">
+        <v>-21.7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>42614</v>
+      </c>
+      <c r="B76" s="7">
+        <v>18.25</v>
+      </c>
+      <c r="C76" s="7">
+        <v>17.95</v>
+      </c>
+      <c r="D76" s="7">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="E76" s="7">
+        <v>17.05</v>
+      </c>
+      <c r="F76" s="10">
+        <v>-1.35</v>
+      </c>
+      <c r="G76" s="10">
+        <v>-6.99</v>
+      </c>
+      <c r="H76" s="9">
+        <v>0.152</v>
+      </c>
+      <c r="I76" s="10">
+        <v>-16.100000000000001</v>
+      </c>
+      <c r="J76" s="10">
+        <v>-34.299999999999997</v>
+      </c>
+      <c r="K76" s="9">
+        <v>1.7</v>
+      </c>
+      <c r="L76" s="10">
+        <v>-21.8</v>
+      </c>
+      <c r="M76" s="9">
+        <v>0.152</v>
+      </c>
+      <c r="N76" s="10">
+        <v>-16.100000000000001</v>
+      </c>
+      <c r="O76" s="10">
+        <v>-34.299999999999997</v>
+      </c>
+      <c r="P76" s="9">
+        <v>1.7</v>
+      </c>
+      <c r="Q76" s="10">
+        <v>-21.8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>42583</v>
+      </c>
+      <c r="B77" s="7">
+        <v>18.2</v>
+      </c>
+      <c r="C77" s="7">
+        <v>19.3</v>
+      </c>
+      <c r="D77" s="7">
+        <v>19.7</v>
+      </c>
+      <c r="E77" s="7">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="F77" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G77" s="8">
+        <v>6.04</v>
+      </c>
+      <c r="H77" s="9">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="I77" s="8">
+        <v>5.74</v>
+      </c>
+      <c r="J77" s="10">
+        <v>-30.4</v>
+      </c>
+      <c r="K77" s="9">
+        <v>1.55</v>
+      </c>
+      <c r="L77" s="10">
+        <v>-20.3</v>
+      </c>
+      <c r="M77" s="9">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="N77" s="8">
+        <v>5.74</v>
+      </c>
+      <c r="O77" s="10">
+        <v>-30.4</v>
+      </c>
+      <c r="P77" s="9">
+        <v>1.55</v>
+      </c>
+      <c r="Q77" s="10">
+        <v>-20.3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>42552</v>
+      </c>
+      <c r="B78" s="7">
+        <v>18.5</v>
+      </c>
+      <c r="C78" s="7">
+        <v>18.2</v>
+      </c>
+      <c r="D78" s="7">
+        <v>18.95</v>
+      </c>
+      <c r="E78" s="7">
+        <v>17.2</v>
+      </c>
+      <c r="F78" s="10">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="G78" s="10">
+        <v>-2.93</v>
+      </c>
+      <c r="H78" s="9">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="I78" s="10">
+        <v>-5.19</v>
+      </c>
+      <c r="J78" s="10">
+        <v>-17.899999999999999</v>
+      </c>
+      <c r="K78" s="9">
+        <v>1.36</v>
+      </c>
+      <c r="L78" s="10">
+        <v>-18.8</v>
+      </c>
+      <c r="M78" s="9">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="N78" s="10">
+        <v>-5.19</v>
+      </c>
+      <c r="O78" s="10">
+        <v>-17.899999999999999</v>
+      </c>
+      <c r="P78" s="9">
+        <v>1.36</v>
+      </c>
+      <c r="Q78" s="10">
+        <v>-18.8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>42522</v>
+      </c>
+      <c r="B79" s="7">
+        <v>19.850000000000001</v>
+      </c>
+      <c r="C79" s="7">
+        <v>18.75</v>
+      </c>
+      <c r="D79" s="7">
+        <v>19.850000000000001</v>
+      </c>
+      <c r="E79" s="7">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="F79" s="10">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="G79" s="10">
+        <v>-5.54</v>
+      </c>
+      <c r="H79" s="9">
+        <v>0.18</v>
+      </c>
+      <c r="I79" s="10">
+        <v>-19.899999999999999</v>
+      </c>
+      <c r="J79" s="10">
+        <v>-28.4</v>
+      </c>
+      <c r="K79" s="9">
+        <v>1.19</v>
+      </c>
+      <c r="L79" s="10">
+        <v>-18.899999999999999</v>
+      </c>
+      <c r="M79" s="9">
+        <v>0.18</v>
+      </c>
+      <c r="N79" s="10">
+        <v>-19.899999999999999</v>
+      </c>
+      <c r="O79" s="10">
+        <v>-28.4</v>
+      </c>
+      <c r="P79" s="9">
+        <v>1.19</v>
+      </c>
+      <c r="Q79" s="10">
+        <v>-18.899999999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>42491</v>
+      </c>
+      <c r="B80" s="7">
+        <v>19.850000000000001</v>
+      </c>
+      <c r="C80" s="7">
+        <v>19.850000000000001</v>
+      </c>
+      <c r="D80" s="7">
+        <v>20.55</v>
+      </c>
+      <c r="E80" s="7">
+        <v>18</v>
+      </c>
+      <c r="F80" s="10">
+        <v>-0.7</v>
+      </c>
+      <c r="G80" s="10">
+        <v>-3.41</v>
+      </c>
+      <c r="H80" s="9">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="I80" s="8">
+        <v>2.85</v>
+      </c>
+      <c r="J80" s="10">
+        <v>-0.71</v>
+      </c>
+      <c r="K80" s="9">
+        <v>1.01</v>
+      </c>
+      <c r="L80" s="10">
+        <v>-16.899999999999999</v>
+      </c>
+      <c r="M80" s="9">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="N80" s="8">
+        <v>2.85</v>
+      </c>
+      <c r="O80" s="10">
+        <v>-0.71</v>
+      </c>
+      <c r="P80" s="9">
+        <v>1.01</v>
+      </c>
+      <c r="Q80" s="10">
+        <v>-16.899999999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>42461</v>
+      </c>
+      <c r="B81" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="C81" s="7">
+        <v>20.55</v>
+      </c>
+      <c r="D81" s="7">
+        <v>20.9</v>
+      </c>
+      <c r="E81" s="7">
+        <v>20</v>
+      </c>
+      <c r="F81" s="10">
+        <v>-0.45</v>
+      </c>
+      <c r="G81" s="10">
+        <v>-2.14</v>
+      </c>
+      <c r="H81" s="9">
+        <v>0.219</v>
+      </c>
+      <c r="I81" s="8">
+        <v>15</v>
+      </c>
+      <c r="J81" s="10">
+        <v>-10</v>
+      </c>
+      <c r="K81" s="9">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="L81" s="10">
+        <v>-20.6</v>
+      </c>
+      <c r="M81" s="9">
+        <v>0.219</v>
+      </c>
+      <c r="N81" s="8">
+        <v>15</v>
+      </c>
+      <c r="O81" s="10">
+        <v>-10</v>
+      </c>
+      <c r="P81" s="9">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="Q81" s="10">
+        <v>-20.6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>42430</v>
+      </c>
+      <c r="B82" s="7">
+        <v>20.45</v>
+      </c>
+      <c r="C82" s="7">
+        <v>21</v>
+      </c>
+      <c r="D82" s="7">
+        <v>23.65</v>
+      </c>
+      <c r="E82" s="7">
+        <v>20</v>
+      </c>
+      <c r="F82" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="G82" s="8">
+        <v>0.24</v>
+      </c>
+      <c r="H82" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="I82" s="8">
+        <v>4.51</v>
+      </c>
+      <c r="J82" s="10">
+        <v>-28.6</v>
+      </c>
+      <c r="K82" s="9">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="L82" s="10">
+        <v>-24.1</v>
+      </c>
+      <c r="M82" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="N82" s="8">
+        <v>4.51</v>
+      </c>
+      <c r="O82" s="10">
+        <v>-28.6</v>
+      </c>
+      <c r="P82" s="9">
+        <v>0.56899999999999995</v>
+      </c>
+      <c r="Q82" s="10">
+        <v>-24.1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>42401</v>
+      </c>
+      <c r="B83" s="7">
+        <v>21.2</v>
+      </c>
+      <c r="C83" s="7">
+        <v>20.95</v>
+      </c>
+      <c r="D83" s="7">
+        <v>22.65</v>
+      </c>
+      <c r="E83" s="7">
+        <v>19.850000000000001</v>
+      </c>
+      <c r="F83" s="10">
+        <v>-0.4</v>
+      </c>
+      <c r="G83" s="10">
+        <v>-1.87</v>
+      </c>
+      <c r="H83" s="9">
+        <v>0.182</v>
+      </c>
+      <c r="I83" s="10">
+        <v>-7.1</v>
+      </c>
+      <c r="J83" s="10">
+        <v>-16.7</v>
+      </c>
+      <c r="K83" s="9">
+        <v>0.378</v>
+      </c>
+      <c r="L83" s="10">
+        <v>-21.6</v>
+      </c>
+      <c r="M83" s="9">
+        <v>0.182</v>
+      </c>
+      <c r="N83" s="10">
+        <v>-7.1</v>
+      </c>
+      <c r="O83" s="10">
+        <v>-16.7</v>
+      </c>
+      <c r="P83" s="9">
+        <v>0.378</v>
+      </c>
+      <c r="Q83" s="10">
+        <v>-21.6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>42370</v>
+      </c>
+      <c r="B84" s="7">
+        <v>23.35</v>
+      </c>
+      <c r="C84" s="7">
+        <v>21.35</v>
+      </c>
+      <c r="D84" s="7">
+        <v>23.6</v>
+      </c>
+      <c r="E84" s="7">
+        <v>20</v>
+      </c>
+      <c r="F84" s="10">
+        <v>-1.4</v>
+      </c>
+      <c r="G84" s="10">
+        <v>-6.15</v>
+      </c>
+      <c r="H84" s="9">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="I84" s="10">
+        <v>-11.6</v>
+      </c>
+      <c r="J84" s="10">
+        <v>-25.6</v>
+      </c>
+      <c r="K84" s="9">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="L84" s="10">
+        <v>-25.6</v>
+      </c>
+      <c r="M84" s="9">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="N84" s="10">
+        <v>-11.6</v>
+      </c>
+      <c r="O84" s="10">
+        <v>-25.6</v>
+      </c>
+      <c r="P84" s="9">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="Q84" s="10">
+        <v>-25.6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>42339</v>
+      </c>
+      <c r="B85" s="7">
+        <v>25.3</v>
+      </c>
+      <c r="C85" s="7">
+        <v>22.75</v>
+      </c>
+      <c r="D85" s="7">
+        <v>25.3</v>
+      </c>
+      <c r="E85" s="7">
+        <v>21.95</v>
+      </c>
+      <c r="F85" s="10">
+        <v>-2.1</v>
+      </c>
+      <c r="G85" s="10">
+        <v>-8.4499999999999993</v>
+      </c>
+      <c r="H85" s="9">
+        <v>0.222</v>
+      </c>
+      <c r="I85" s="8">
+        <v>7.04</v>
+      </c>
+      <c r="J85" s="8">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="K85" s="9">
+        <v>2.84</v>
+      </c>
+      <c r="L85" s="10">
+        <v>-8.32</v>
+      </c>
+      <c r="M85" s="9">
+        <v>0.222</v>
+      </c>
+      <c r="N85" s="8">
+        <v>7.04</v>
+      </c>
+      <c r="O85" s="8">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="P85" s="9">
+        <v>2.84</v>
+      </c>
+      <c r="Q85" s="10">
+        <v>-8.32</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>42309</v>
+      </c>
+      <c r="B86" s="7">
+        <v>22.15</v>
+      </c>
+      <c r="C86" s="7">
+        <v>24.85</v>
+      </c>
+      <c r="D86" s="7">
+        <v>25.25</v>
+      </c>
+      <c r="E86" s="7">
+        <v>22.1</v>
+      </c>
+      <c r="F86" s="8">
+        <v>0.35</v>
+      </c>
+      <c r="G86" s="8">
+        <v>1.43</v>
+      </c>
+      <c r="H86" s="9">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="I86" s="10">
+        <v>-12.8</v>
+      </c>
+      <c r="J86" s="10">
+        <v>-5.96</v>
+      </c>
+      <c r="K86" s="9">
+        <v>2.62</v>
+      </c>
+      <c r="L86" s="10">
+        <v>-9.24</v>
+      </c>
+      <c r="M86" s="9">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N86" s="10">
+        <v>-12.8</v>
+      </c>
+      <c r="O86" s="10">
+        <v>-5.96</v>
+      </c>
+      <c r="P86" s="9">
+        <v>2.62</v>
+      </c>
+      <c r="Q86" s="10">
+        <v>-9.24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>42278</v>
+      </c>
+      <c r="B87" s="7">
+        <v>24.55</v>
+      </c>
+      <c r="C87" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="D87" s="7">
+        <v>24.9</v>
+      </c>
+      <c r="E87" s="7">
+        <v>21</v>
+      </c>
+      <c r="F87" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="G87" s="8">
+        <v>6.99</v>
+      </c>
+      <c r="H87" s="9">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="I87" s="8">
+        <v>2.84</v>
+      </c>
+      <c r="J87" s="10">
+        <v>-5.49</v>
+      </c>
+      <c r="K87" s="9">
+        <v>2.41</v>
+      </c>
+      <c r="L87" s="10">
+        <v>-9.51</v>
+      </c>
+      <c r="M87" s="9">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="N87" s="8">
+        <v>2.84</v>
+      </c>
+      <c r="O87" s="10">
+        <v>-5.49</v>
+      </c>
+      <c r="P87" s="9">
+        <v>2.41</v>
+      </c>
+      <c r="Q87" s="10">
+        <v>-9.51</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>42248</v>
+      </c>
+      <c r="B88" s="7">
+        <v>22.25</v>
+      </c>
+      <c r="C88" s="7">
+        <v>22.9</v>
+      </c>
+      <c r="D88" s="7">
+        <v>23.6</v>
+      </c>
+      <c r="E88" s="7">
+        <v>20.75</v>
+      </c>
+      <c r="F88" s="10">
+        <v>-1.7</v>
+      </c>
+      <c r="G88" s="10">
+        <v>-6.91</v>
+      </c>
+      <c r="H88" s="9">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="I88" s="10">
+        <v>-11</v>
+      </c>
+      <c r="J88" s="10">
+        <v>-18.5</v>
+      </c>
+      <c r="K88" s="9">
+        <v>2.17</v>
+      </c>
+      <c r="L88" s="10">
+        <v>-9.93</v>
+      </c>
+      <c r="M88" s="9">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="N88" s="10">
+        <v>-11</v>
+      </c>
+      <c r="O88" s="10">
+        <v>-18.5</v>
+      </c>
+      <c r="P88" s="9">
+        <v>2.17</v>
+      </c>
+      <c r="Q88" s="10">
+        <v>-9.93</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>42217</v>
+      </c>
+      <c r="B89" s="7">
+        <v>25.75</v>
+      </c>
+      <c r="C89" s="7">
+        <v>24.6</v>
+      </c>
+      <c r="D89" s="7">
+        <v>27.05</v>
+      </c>
+      <c r="E89" s="7">
+        <v>20.25</v>
+      </c>
+      <c r="F89" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="G89" s="10">
+        <v>-0.4</v>
+      </c>
+      <c r="H89" s="9">
+        <v>0.26</v>
+      </c>
+      <c r="I89" s="8">
+        <v>24.7</v>
+      </c>
+      <c r="J89" s="10">
+        <v>-12.1</v>
+      </c>
+      <c r="K89" s="9">
+        <v>1.94</v>
+      </c>
+      <c r="L89" s="10">
+        <v>-8.7899999999999991</v>
+      </c>
+      <c r="M89" s="9">
+        <v>0.26</v>
+      </c>
+      <c r="N89" s="8">
+        <v>24.7</v>
+      </c>
+      <c r="O89" s="10">
+        <v>-12.1</v>
+      </c>
+      <c r="P89" s="9">
+        <v>1.94</v>
+      </c>
+      <c r="Q89" s="10">
+        <v>-8.7899999999999991</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>42186</v>
+      </c>
+      <c r="B90" s="7">
+        <v>24.05</v>
+      </c>
+      <c r="C90" s="7">
+        <v>24.7</v>
+      </c>
+      <c r="D90" s="7">
+        <v>27.2</v>
+      </c>
+      <c r="E90" s="7">
+        <v>22.4</v>
+      </c>
+      <c r="F90" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="G90" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="H90" s="9">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="I90" s="10">
+        <v>-17.399999999999999</v>
+      </c>
+      <c r="J90" s="10">
+        <v>-16.3</v>
+      </c>
+      <c r="K90" s="9">
+        <v>1.68</v>
+      </c>
+      <c r="L90" s="10">
+        <v>-8.26</v>
+      </c>
+      <c r="M90" s="9">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="N90" s="10">
+        <v>-17.399999999999999</v>
+      </c>
+      <c r="O90" s="10">
+        <v>-16.3</v>
+      </c>
+      <c r="P90" s="9">
+        <v>1.68</v>
+      </c>
+      <c r="Q90" s="10">
+        <v>-8.26</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>42156</v>
+      </c>
+      <c r="B91" s="7">
+        <v>23.1</v>
+      </c>
+      <c r="C91" s="7">
+        <v>24.05</v>
+      </c>
+      <c r="D91" s="7">
+        <v>24.45</v>
+      </c>
+      <c r="E91" s="7">
+        <v>21.95</v>
+      </c>
+      <c r="F91" s="8">
+        <v>0.95</v>
+      </c>
+      <c r="G91" s="8">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="H91" s="9">
+        <v>0.252</v>
+      </c>
+      <c r="I91" s="8">
+        <v>11.2</v>
+      </c>
+      <c r="J91" s="8">
+        <v>1.48</v>
+      </c>
+      <c r="K91" s="9">
+        <v>1.47</v>
+      </c>
+      <c r="L91" s="10">
+        <v>-6.98</v>
+      </c>
+      <c r="M91" s="9">
+        <v>0.252</v>
+      </c>
+      <c r="N91" s="8">
+        <v>11.2</v>
+      </c>
+      <c r="O91" s="8">
+        <v>1.48</v>
+      </c>
+      <c r="P91" s="9">
+        <v>1.47</v>
+      </c>
+      <c r="Q91" s="10">
+        <v>-6.98</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>42125</v>
+      </c>
+      <c r="B92" s="7">
+        <v>23.3</v>
+      </c>
+      <c r="C92" s="7">
+        <v>23.1</v>
+      </c>
+      <c r="D92" s="7">
+        <v>25</v>
+      </c>
+      <c r="E92" s="7">
+        <v>22.65</v>
+      </c>
+      <c r="F92" s="10">
+        <v>-0.85</v>
+      </c>
+      <c r="G92" s="10">
+        <v>-3.55</v>
+      </c>
+      <c r="H92" s="9">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="I92" s="10">
+        <v>-6.82</v>
+      </c>
+      <c r="J92" s="10">
+        <v>-14.7</v>
+      </c>
+      <c r="K92" s="9">
+        <v>1.22</v>
+      </c>
+      <c r="L92" s="10">
+        <v>-8.56</v>
+      </c>
+      <c r="M92" s="9">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="N92" s="10">
+        <v>-6.82</v>
+      </c>
+      <c r="O92" s="10">
+        <v>-14.7</v>
+      </c>
+      <c r="P92" s="9">
+        <v>1.22</v>
+      </c>
+      <c r="Q92" s="10">
+        <v>-8.56</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>42095</v>
+      </c>
+      <c r="B93" s="7">
+        <v>24.2</v>
+      </c>
+      <c r="C93" s="7">
+        <v>23.95</v>
+      </c>
+      <c r="D93" s="7">
+        <v>25.4</v>
+      </c>
+      <c r="E93" s="7">
+        <v>23.25</v>
+      </c>
+      <c r="F93" s="10">
+        <v>-0.95</v>
+      </c>
+      <c r="G93" s="10">
+        <v>-3.82</v>
+      </c>
+      <c r="H93" s="9">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="I93" s="10">
+        <v>-8.68</v>
+      </c>
+      <c r="J93" s="10">
+        <v>-17</v>
+      </c>
+      <c r="K93" s="9">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="L93" s="10">
+        <v>-7.04</v>
+      </c>
+      <c r="M93" s="9">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="N93" s="10">
+        <v>-8.68</v>
+      </c>
+      <c r="O93" s="10">
+        <v>-17</v>
+      </c>
+      <c r="P93" s="9">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="Q93" s="10">
+        <v>-7.04</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>42064</v>
+      </c>
+      <c r="B94" s="7">
+        <v>24.85</v>
+      </c>
+      <c r="C94" s="7">
+        <v>24.9</v>
+      </c>
+      <c r="D94" s="7">
+        <v>28</v>
+      </c>
+      <c r="E94" s="7">
+        <v>24.05</v>
+      </c>
+      <c r="F94" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="G94" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="H94" s="9">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="I94" s="8">
+        <v>21.9</v>
+      </c>
+      <c r="J94" s="10">
+        <v>-4.5199999999999996</v>
+      </c>
+      <c r="K94" s="9">
+        <v>0.749</v>
+      </c>
+      <c r="L94" s="10">
+        <v>-3.26</v>
+      </c>
+      <c r="M94" s="9">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="N94" s="8">
+        <v>21.9</v>
+      </c>
+      <c r="O94" s="10">
+        <v>-4.5199999999999996</v>
+      </c>
+      <c r="P94" s="9">
+        <v>0.749</v>
+      </c>
+      <c r="Q94" s="10">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>42036</v>
+      </c>
+      <c r="B95" s="7">
+        <v>24</v>
+      </c>
+      <c r="C95" s="7">
+        <v>24.85</v>
+      </c>
+      <c r="D95" s="7">
+        <v>24.9</v>
+      </c>
+      <c r="E95" s="7">
+        <v>24</v>
+      </c>
+      <c r="F95" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="G95" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="H95" s="9">
+        <v>0.219</v>
+      </c>
+      <c r="I95" s="10">
+        <v>-17</v>
+      </c>
+      <c r="J95" s="10">
+        <v>-10.9</v>
+      </c>
+      <c r="K95" s="9">
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="L95" s="10">
+        <v>-2.5499999999999998</v>
+      </c>
+      <c r="M95" s="9">
+        <v>0.219</v>
+      </c>
+      <c r="N95" s="10">
+        <v>-17</v>
+      </c>
+      <c r="O95" s="10">
+        <v>-10.9</v>
+      </c>
+      <c r="P95" s="9">
+        <v>0.48199999999999998</v>
+      </c>
+      <c r="Q95" s="10">
+        <v>-2.5499999999999998</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>42005</v>
+      </c>
+      <c r="B96" s="7">
+        <v>25.3</v>
+      </c>
+      <c r="C96" s="7">
+        <v>24.75</v>
+      </c>
+      <c r="D96" s="7">
+        <v>26.75</v>
+      </c>
+      <c r="E96" s="7">
+        <v>24</v>
+      </c>
+      <c r="F96" s="10">
+        <v>-0.45</v>
+      </c>
+      <c r="G96" s="10">
+        <v>-1.79</v>
+      </c>
+      <c r="H96" s="9">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="I96" s="8">
+        <v>23.7</v>
+      </c>
+      <c r="J96" s="8">
+        <v>5.62</v>
+      </c>
+      <c r="K96" s="9">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="L96" s="8">
+        <v>5.62</v>
+      </c>
+      <c r="M96" s="9">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="N96" s="8">
+        <v>23.7</v>
+      </c>
+      <c r="O96" s="8">
+        <v>5.62</v>
+      </c>
+      <c r="P96" s="9">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="Q96" s="8">
+        <v>5.62</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>41974</v>
+      </c>
+      <c r="B97" s="7">
+        <v>24.4</v>
+      </c>
+      <c r="C97" s="7">
+        <v>25.2</v>
+      </c>
+      <c r="D97" s="7">
+        <v>27.3</v>
+      </c>
+      <c r="E97" s="7">
+        <v>23.2</v>
+      </c>
+      <c r="F97" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="G97" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="H97" s="9">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="I97" s="10">
+        <v>-3.31</v>
+      </c>
+      <c r="J97" s="10">
+        <v>-15.1</v>
+      </c>
+      <c r="K97" s="9">
+        <v>3.1</v>
+      </c>
+      <c r="L97" s="10">
+        <v>-7.21</v>
+      </c>
+      <c r="M97" s="9">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="N97" s="10">
+        <v>-3.31</v>
+      </c>
+      <c r="O97" s="10">
+        <v>-15.1</v>
+      </c>
+      <c r="P97" s="9">
+        <v>3.1</v>
+      </c>
+      <c r="Q97" s="10">
+        <v>-7.21</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>41944</v>
+      </c>
+      <c r="B98" s="7">
+        <v>27.95</v>
+      </c>
+      <c r="C98" s="7">
+        <v>24.9</v>
+      </c>
+      <c r="D98" s="7">
+        <v>28.15</v>
+      </c>
+      <c r="E98" s="7">
+        <v>24.9</v>
+      </c>
+      <c r="F98" s="10">
+        <v>-3.3</v>
+      </c>
+      <c r="G98" s="10">
+        <v>-11.7</v>
+      </c>
+      <c r="H98" s="9">
+        <v>0.221</v>
+      </c>
+      <c r="I98" s="10">
+        <v>-12.3</v>
+      </c>
+      <c r="J98" s="10">
+        <v>-23.6</v>
+      </c>
+      <c r="K98" s="9">
+        <v>2.88</v>
+      </c>
+      <c r="L98" s="10">
+        <v>-6.57</v>
+      </c>
+      <c r="M98" s="9">
+        <v>0.221</v>
+      </c>
+      <c r="N98" s="10">
+        <v>-12.3</v>
+      </c>
+      <c r="O98" s="10">
+        <v>-23.6</v>
+      </c>
+      <c r="P98" s="9">
+        <v>2.88</v>
+      </c>
+      <c r="Q98" s="10">
+        <v>-6.57</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>41913</v>
+      </c>
+      <c r="B99" s="7">
+        <v>27.55</v>
+      </c>
+      <c r="C99" s="7">
+        <v>28.2</v>
+      </c>
+      <c r="D99" s="7">
+        <v>28.3</v>
+      </c>
+      <c r="E99" s="7">
+        <v>26.05</v>
+      </c>
+      <c r="F99" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="G99" s="8">
+        <v>0.71</v>
+      </c>
+      <c r="H99" s="9">
+        <v>0.252</v>
+      </c>
+      <c r="I99" s="10">
+        <v>-11.3</v>
+      </c>
+      <c r="J99" s="10">
+        <v>-9.99</v>
+      </c>
+      <c r="K99" s="9">
+        <v>2.66</v>
+      </c>
+      <c r="L99" s="10">
+        <v>-4.8099999999999996</v>
+      </c>
+      <c r="M99" s="9">
+        <v>0.252</v>
+      </c>
+      <c r="N99" s="10">
+        <v>-11.3</v>
+      </c>
+      <c r="O99" s="10">
+        <v>-9.99</v>
+      </c>
+      <c r="P99" s="9">
+        <v>2.66</v>
+      </c>
+      <c r="Q99" s="10">
+        <v>-4.8099999999999996</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>41883</v>
+      </c>
+      <c r="B100" s="7">
+        <v>29</v>
+      </c>
+      <c r="C100" s="7">
+        <v>28</v>
+      </c>
+      <c r="D100" s="7">
+        <v>29.8</v>
+      </c>
+      <c r="E100" s="7">
+        <v>27.85</v>
+      </c>
+      <c r="F100" s="10">
+        <v>-1.5</v>
+      </c>
+      <c r="G100" s="10">
+        <v>-5.08</v>
+      </c>
+      <c r="H100" s="9">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="I100" s="10">
+        <v>-4.01</v>
+      </c>
+      <c r="J100" s="10">
+        <v>-1.8</v>
+      </c>
+      <c r="K100" s="9">
+        <v>2.41</v>
+      </c>
+      <c r="L100" s="10">
+        <v>-4.24</v>
+      </c>
+      <c r="M100" s="9">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="N100" s="10">
+        <v>-4.01</v>
+      </c>
+      <c r="O100" s="10">
+        <v>-1.8</v>
+      </c>
+      <c r="P100" s="9">
+        <v>2.41</v>
+      </c>
+      <c r="Q100" s="10">
+        <v>-4.24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>41852</v>
+      </c>
+      <c r="B101" s="7">
+        <v>29.55</v>
+      </c>
+      <c r="C101" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="D101" s="7">
+        <v>31.45</v>
+      </c>
+      <c r="E101" s="7">
+        <v>27.95</v>
+      </c>
+      <c r="F101" s="10">
+        <v>-0.5</v>
+      </c>
+      <c r="G101" s="10">
+        <v>-1.67</v>
+      </c>
+      <c r="H101" s="9">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="I101" s="8">
+        <v>18.7</v>
+      </c>
+      <c r="J101" s="8">
+        <v>16</v>
+      </c>
+      <c r="K101" s="9">
+        <v>2.13</v>
+      </c>
+      <c r="L101" s="10">
+        <v>-4.5599999999999996</v>
+      </c>
+      <c r="M101" s="9">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="N101" s="8">
+        <v>18.7</v>
+      </c>
+      <c r="O101" s="8">
+        <v>16</v>
+      </c>
+      <c r="P101" s="9">
+        <v>2.13</v>
+      </c>
+      <c r="Q101" s="10">
+        <v>-4.5599999999999996</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>41821</v>
+      </c>
+      <c r="B102" s="7">
+        <v>29.9</v>
+      </c>
+      <c r="C102" s="7">
+        <v>30</v>
+      </c>
+      <c r="D102" s="7">
+        <v>31.35</v>
+      </c>
+      <c r="E102" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="F102" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="G102" s="8">
+        <v>0.33</v>
+      </c>
+      <c r="H102" s="9">
+        <v>0.249</v>
+      </c>
+      <c r="I102" s="8">
+        <v>0.21</v>
+      </c>
+      <c r="J102" s="10">
+        <v>-5.66</v>
+      </c>
+      <c r="K102" s="9">
+        <v>1.83</v>
+      </c>
+      <c r="L102" s="10">
+        <v>-7.21</v>
+      </c>
+      <c r="M102" s="9">
+        <v>0.249</v>
+      </c>
+      <c r="N102" s="8">
+        <v>0.21</v>
+      </c>
+      <c r="O102" s="10">
+        <v>-5.66</v>
+      </c>
+      <c r="P102" s="9">
+        <v>1.83</v>
+      </c>
+      <c r="Q102" s="10">
+        <v>-7.21</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>41791</v>
+      </c>
+      <c r="B103" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="C103" s="7">
+        <v>29.9</v>
+      </c>
+      <c r="D103" s="7">
+        <v>31.65</v>
+      </c>
+      <c r="E103" s="7">
+        <v>29.55</v>
+      </c>
+      <c r="F103" s="10">
+        <v>-1.05</v>
+      </c>
+      <c r="G103" s="10">
+        <v>-3.39</v>
+      </c>
+      <c r="H103" s="9">
+        <v>0.248</v>
+      </c>
+      <c r="I103" s="10">
+        <v>-6.55</v>
+      </c>
+      <c r="J103" s="10">
+        <v>-11.3</v>
+      </c>
+      <c r="K103" s="9">
+        <v>1.58</v>
+      </c>
+      <c r="L103" s="10">
+        <v>-7.45</v>
+      </c>
+      <c r="M103" s="9">
+        <v>0.248</v>
+      </c>
+      <c r="N103" s="10">
+        <v>-6.55</v>
+      </c>
+      <c r="O103" s="10">
+        <v>-11.3</v>
+      </c>
+      <c r="P103" s="9">
+        <v>1.58</v>
+      </c>
+      <c r="Q103" s="10">
+        <v>-7.45</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>41760</v>
+      </c>
+      <c r="B104" s="7">
+        <v>30.9</v>
+      </c>
+      <c r="C104" s="7">
+        <v>30.95</v>
+      </c>
+      <c r="D104" s="7">
+        <v>32.9</v>
+      </c>
+      <c r="E104" s="7">
+        <v>30</v>
+      </c>
+      <c r="F104" s="10">
+        <v>-1.05</v>
+      </c>
+      <c r="G104" s="10">
+        <v>-3.28</v>
+      </c>
+      <c r="H104" s="9">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="I104" s="10">
+        <v>-9.36</v>
+      </c>
+      <c r="J104" s="10">
+        <v>-14</v>
+      </c>
+      <c r="K104" s="9">
+        <v>1.33</v>
+      </c>
+      <c r="L104" s="10">
+        <v>-6.7</v>
+      </c>
+      <c r="M104" s="9">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="N104" s="10">
+        <v>-9.36</v>
+      </c>
+      <c r="O104" s="10">
+        <v>-14</v>
+      </c>
+      <c r="P104" s="9">
+        <v>1.33</v>
+      </c>
+      <c r="Q104" s="10">
+        <v>-6.7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>41730</v>
+      </c>
+      <c r="B105" s="7">
+        <v>32.9</v>
+      </c>
+      <c r="C105" s="7">
+        <v>32</v>
+      </c>
+      <c r="D105" s="7">
+        <v>34.450000000000003</v>
+      </c>
+      <c r="E105" s="7">
+        <v>30.55</v>
+      </c>
+      <c r="F105" s="10">
+        <v>-0.9</v>
+      </c>
+      <c r="G105" s="10">
+        <v>-2.74</v>
+      </c>
+      <c r="H105" s="9">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="I105" s="8">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="J105" s="8">
+        <v>10.7</v>
+      </c>
+      <c r="K105" s="9">
+        <v>1.07</v>
+      </c>
+      <c r="L105" s="10">
+        <v>-4.68</v>
+      </c>
+      <c r="M105" s="9">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="N105" s="8">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="O105" s="8">
+        <v>10.7</v>
+      </c>
+      <c r="P105" s="9">
+        <v>1.07</v>
+      </c>
+      <c r="Q105" s="10">
+        <v>-4.68</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>41699</v>
+      </c>
+      <c r="B106" s="7">
+        <v>29.8</v>
+      </c>
+      <c r="C106" s="7">
+        <v>32.9</v>
+      </c>
+      <c r="D106" s="7">
+        <v>39.5</v>
+      </c>
+      <c r="E106" s="7">
+        <v>29.6</v>
+      </c>
+      <c r="F106" s="8">
+        <v>3.05</v>
+      </c>
+      <c r="G106" s="8">
+        <v>10.220000000000001</v>
+      </c>
+      <c r="H106" s="9">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="I106" s="8">
+        <v>13.8</v>
+      </c>
+      <c r="J106" s="10">
+        <v>-15.9</v>
+      </c>
+      <c r="K106" s="9">
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="L106" s="10">
+        <v>-9.44</v>
+      </c>
+      <c r="M106" s="9">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="N106" s="8">
+        <v>13.8</v>
+      </c>
+      <c r="O106" s="10">
+        <v>-15.9</v>
+      </c>
+      <c r="P106" s="9">
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="Q106" s="10">
+        <v>-9.44</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>41671</v>
+      </c>
+      <c r="B107" s="7">
+        <v>30.4</v>
+      </c>
+      <c r="C107" s="7">
+        <v>29.85</v>
+      </c>
+      <c r="D107" s="7">
+        <v>30.9</v>
+      </c>
+      <c r="E107" s="7">
+        <v>29</v>
+      </c>
+      <c r="F107" s="9">
+        <v>0</v>
+      </c>
+      <c r="G107" s="9">
+        <v>0</v>
+      </c>
+      <c r="H107" s="9">
+        <v>0.245</v>
+      </c>
+      <c r="I107" s="10">
+        <v>-1.7</v>
+      </c>
+      <c r="J107" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="K107" s="9">
+        <v>0.495</v>
+      </c>
+      <c r="L107" s="10">
+        <v>-5.36</v>
+      </c>
+      <c r="M107" s="9">
+        <v>0.245</v>
+      </c>
+      <c r="N107" s="10">
+        <v>-1.7</v>
+      </c>
+      <c r="O107" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="P107" s="9">
+        <v>0.495</v>
+      </c>
+      <c r="Q107" s="10">
+        <v>-5.36</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>41640</v>
+      </c>
+      <c r="B108" s="7">
+        <v>32</v>
+      </c>
+      <c r="C108" s="7">
+        <v>29.85</v>
+      </c>
+      <c r="D108" s="7">
+        <v>32.6</v>
+      </c>
+      <c r="E108" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="F108" s="10">
+        <v>-2.5499999999999998</v>
+      </c>
+      <c r="G108" s="10">
+        <v>-7.87</v>
+      </c>
+      <c r="H108" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="I108" s="10">
+        <v>-0.6</v>
+      </c>
+      <c r="J108" s="10">
+        <v>-11.1</v>
+      </c>
+      <c r="K108" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="L108" s="10">
+        <v>-11.1</v>
+      </c>
+      <c r="M108" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="N108" s="10">
+        <v>-0.6</v>
+      </c>
+      <c r="O108" s="10">
+        <v>-11.1</v>
+      </c>
+      <c r="P108" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="Q108" s="10">
+        <v>-11.1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>41609</v>
+      </c>
+      <c r="B109" s="7">
+        <v>28.1</v>
+      </c>
+      <c r="C109" s="7">
+        <v>32.4</v>
+      </c>
+      <c r="D109" s="7">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="E109" s="7">
+        <v>28</v>
+      </c>
+      <c r="F109" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="G109" s="8">
+        <v>15.3</v>
+      </c>
+      <c r="H109" s="9">
+        <v>0.251</v>
+      </c>
+      <c r="I109" s="10">
+        <v>-12.9</v>
+      </c>
+      <c r="J109" s="10">
+        <v>-10.1</v>
+      </c>
+      <c r="K109" s="9">
+        <v>3.34</v>
+      </c>
+      <c r="L109" s="8">
+        <v>5.12</v>
+      </c>
+      <c r="M109" s="9">
+        <v>0.251</v>
+      </c>
+      <c r="N109" s="10">
+        <v>-12.9</v>
+      </c>
+      <c r="O109" s="10">
+        <v>-10.1</v>
+      </c>
+      <c r="P109" s="9">
+        <v>3.34</v>
+      </c>
+      <c r="Q109" s="8">
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>41579</v>
+      </c>
+      <c r="B110" s="7">
+        <v>28</v>
+      </c>
+      <c r="C110" s="7">
+        <v>28.1</v>
+      </c>
+      <c r="D110" s="7">
+        <v>29.2</v>
+      </c>
+      <c r="E110" s="7">
+        <v>27</v>
+      </c>
+      <c r="F110" s="9">
+        <v>0</v>
+      </c>
+      <c r="G110" s="9">
+        <v>0</v>
+      </c>
+      <c r="H110" s="9">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="I110" s="8">
+        <v>3.21</v>
+      </c>
+      <c r="J110" s="8">
+        <v>0.68</v>
+      </c>
+      <c r="K110" s="9">
+        <v>3.08</v>
+      </c>
+      <c r="L110" s="8">
+        <v>6.58</v>
+      </c>
+      <c r="M110" s="9">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="N110" s="8">
+        <v>3.21</v>
+      </c>
+      <c r="O110" s="8">
+        <v>0.68</v>
+      </c>
+      <c r="P110" s="9">
+        <v>3.08</v>
+      </c>
+      <c r="Q110" s="8">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
+        <v>41548</v>
+      </c>
+      <c r="B111" s="7">
+        <v>28</v>
+      </c>
+      <c r="C111" s="7">
+        <v>28.1</v>
+      </c>
+      <c r="D111" s="7">
+        <v>29.15</v>
+      </c>
+      <c r="E111" s="7">
+        <v>28</v>
+      </c>
+      <c r="F111" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="G111" s="8">
+        <v>0.36</v>
+      </c>
+      <c r="H111" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I111" s="10">
+        <v>-3.23</v>
+      </c>
+      <c r="J111" s="10">
+        <v>-3.6</v>
+      </c>
+      <c r="K111" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="L111" s="8">
+        <v>7.23</v>
+      </c>
+      <c r="M111" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N111" s="10">
+        <v>-3.23</v>
+      </c>
+      <c r="O111" s="10">
+        <v>-3.6</v>
+      </c>
+      <c r="P111" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="Q111" s="8">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>41518</v>
+      </c>
+      <c r="B112" s="7">
+        <v>29.8</v>
+      </c>
+      <c r="C112" s="7">
+        <v>28</v>
+      </c>
+      <c r="D112" s="7">
+        <v>29.8</v>
+      </c>
+      <c r="E112" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="F112" s="10">
+        <v>-1.8</v>
+      </c>
+      <c r="G112" s="10">
+        <v>-6.04</v>
+      </c>
+      <c r="H112" s="9">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="I112" s="8">
+        <v>13.4</v>
+      </c>
+      <c r="J112" s="10">
+        <v>-2.29</v>
+      </c>
+      <c r="K112" s="9">
+        <v>2.52</v>
+      </c>
+      <c r="L112" s="8">
+        <v>8.59</v>
+      </c>
+      <c r="M112" s="9">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="N112" s="8">
+        <v>13.4</v>
+      </c>
+      <c r="O112" s="10">
+        <v>-2.29</v>
+      </c>
+      <c r="P112" s="9">
+        <v>2.52</v>
+      </c>
+      <c r="Q112" s="8">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
+        <v>41487</v>
+      </c>
+      <c r="B113" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="C113" s="7">
+        <v>29.8</v>
+      </c>
+      <c r="D113" s="7">
+        <v>30.55</v>
+      </c>
+      <c r="E113" s="7">
+        <v>29.15</v>
+      </c>
+      <c r="F113" s="10">
+        <v>-0.7</v>
+      </c>
+      <c r="G113" s="10">
+        <v>-2.2999999999999998</v>
+      </c>
+      <c r="H113" s="9">
+        <v>0.255</v>
+      </c>
+      <c r="I113" s="10">
+        <v>-3.47</v>
+      </c>
+      <c r="J113" s="10">
+        <v>-14.8</v>
+      </c>
+      <c r="K113" s="9">
+        <v>2.23</v>
+      </c>
+      <c r="L113" s="8">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="M113" s="9">
+        <v>0.255</v>
+      </c>
+      <c r="N113" s="10">
+        <v>-3.47</v>
+      </c>
+      <c r="O113" s="10">
+        <v>-14.8</v>
+      </c>
+      <c r="P113" s="9">
+        <v>2.23</v>
+      </c>
+      <c r="Q113" s="8">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>41456</v>
+      </c>
+      <c r="B114" s="7">
+        <v>30.4</v>
+      </c>
+      <c r="C114" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="D114" s="7">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="E114" s="7">
+        <v>28.45</v>
+      </c>
+      <c r="F114" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="G114" s="8">
+        <v>3.04</v>
+      </c>
+      <c r="H114" s="9">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="I114" s="10">
+        <v>-5.73</v>
+      </c>
+      <c r="J114" s="10">
+        <v>-9.6999999999999993</v>
+      </c>
+      <c r="K114" s="9">
+        <v>1.97</v>
+      </c>
+      <c r="L114" s="8">
+        <v>14.5</v>
+      </c>
+      <c r="M114" s="9">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="N114" s="10">
+        <v>-5.74</v>
+      </c>
+      <c r="O114" s="10">
+        <v>-9.6999999999999993</v>
+      </c>
+      <c r="P114" s="9">
+        <v>1.97</v>
+      </c>
+      <c r="Q114" s="8">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
+        <v>41426</v>
+      </c>
+      <c r="B115" s="7">
+        <v>28.8</v>
+      </c>
+      <c r="C115" s="7">
+        <v>29.6</v>
+      </c>
+      <c r="D115" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="E115" s="7">
+        <v>28.8</v>
+      </c>
+      <c r="F115" s="10">
+        <v>-0.4</v>
+      </c>
+      <c r="G115" s="10">
+        <v>-1.33</v>
+      </c>
+      <c r="H115" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I115" s="10">
+        <v>-9.4700000000000006</v>
+      </c>
+      <c r="J115" s="8">
+        <v>24.2</v>
+      </c>
+      <c r="K115" s="9">
+        <v>1.71</v>
+      </c>
+      <c r="L115" s="8">
+        <v>19.5</v>
+      </c>
+      <c r="M115" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N115" s="10">
+        <v>-9.4700000000000006</v>
+      </c>
+      <c r="O115" s="8">
+        <v>24.2</v>
+      </c>
+      <c r="P115" s="9">
+        <v>1.71</v>
+      </c>
+      <c r="Q115" s="8">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>41395</v>
+      </c>
+      <c r="B116" s="7">
+        <v>29.4</v>
+      </c>
+      <c r="C116" s="7">
+        <v>30</v>
+      </c>
+      <c r="D116" s="7">
+        <v>30.45</v>
+      </c>
+      <c r="E116" s="7">
+        <v>28.2</v>
+      </c>
+      <c r="F116" s="8">
+        <v>1</v>
+      </c>
+      <c r="G116" s="8">
+        <v>3.45</v>
+      </c>
+      <c r="H116" s="9">
+        <v>0.309</v>
+      </c>
+      <c r="I116" s="8">
+        <v>16.7</v>
+      </c>
+      <c r="J116" s="8">
+        <v>21.4</v>
+      </c>
+      <c r="K116" s="9">
+        <v>1.43</v>
+      </c>
+      <c r="L116" s="8">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="M116" s="9">
+        <v>0.309</v>
+      </c>
+      <c r="N116" s="8">
+        <v>16.7</v>
+      </c>
+      <c r="O116" s="8">
+        <v>21.4</v>
+      </c>
+      <c r="P116" s="9">
+        <v>1.43</v>
+      </c>
+      <c r="Q116" s="8">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
+        <v>41365</v>
+      </c>
+      <c r="B117" s="7">
+        <v>28.85</v>
+      </c>
+      <c r="C117" s="7">
+        <v>29</v>
+      </c>
+      <c r="D117" s="7">
+        <v>30.45</v>
+      </c>
+      <c r="E117" s="7">
+        <v>28.05</v>
+      </c>
+      <c r="F117" s="8">
+        <v>0.15</v>
+      </c>
+      <c r="G117" s="8">
+        <v>0.52</v>
+      </c>
+      <c r="H117" s="9">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="I117" s="10">
+        <v>-20.100000000000001</v>
+      </c>
+      <c r="J117" s="10">
+        <v>-0.77</v>
+      </c>
+      <c r="K117" s="9">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="L117" s="8">
+        <v>17.8</v>
+      </c>
+      <c r="M117" s="9">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="N117" s="10">
+        <v>-20.100000000000001</v>
+      </c>
+      <c r="O117" s="10">
+        <v>-0.77</v>
+      </c>
+      <c r="P117" s="9">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="Q117" s="8">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>41334</v>
+      </c>
+      <c r="B118" s="7">
+        <v>29</v>
+      </c>
+      <c r="C118" s="7">
+        <v>28.85</v>
+      </c>
+      <c r="D118" s="7">
+        <v>29.6</v>
+      </c>
+      <c r="E118" s="7">
+        <v>28</v>
+      </c>
+      <c r="F118" s="10">
+        <v>-0.85</v>
+      </c>
+      <c r="G118" s="10">
+        <v>-2.86</v>
+      </c>
+      <c r="H118" s="9">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="I118" s="8">
+        <v>37</v>
+      </c>
+      <c r="J118" s="8">
+        <v>35.4</v>
+      </c>
+      <c r="K118" s="9">
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="L118" s="8">
+        <v>25.1</v>
+      </c>
+      <c r="M118" s="9">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="N118" s="8">
+        <v>37</v>
+      </c>
+      <c r="O118" s="8">
+        <v>35.4</v>
+      </c>
+      <c r="P118" s="9">
+        <v>0.85499999999999998</v>
+      </c>
+      <c r="Q118" s="8">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>41306</v>
+      </c>
+      <c r="B119" s="7">
+        <v>30.25</v>
+      </c>
+      <c r="C119" s="7">
+        <v>29.7</v>
+      </c>
+      <c r="D119" s="7">
+        <v>30.85</v>
+      </c>
+      <c r="E119" s="7">
+        <v>28.3</v>
+      </c>
+      <c r="F119" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G119" s="8">
+        <v>1.89</v>
+      </c>
+      <c r="H119" s="9">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="I119" s="10">
+        <v>-13.8</v>
+      </c>
+      <c r="J119" s="10">
+        <v>-6.61</v>
+      </c>
+      <c r="K119" s="9">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="L119" s="8">
+        <v>19.3</v>
+      </c>
+      <c r="M119" s="9">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="N119" s="10">
+        <v>-13.8</v>
+      </c>
+      <c r="O119" s="10">
+        <v>-6.62</v>
+      </c>
+      <c r="P119" s="9">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="Q119" s="8">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>41275</v>
+      </c>
+      <c r="B120" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="C120" s="7">
+        <v>29.15</v>
+      </c>
+      <c r="D120" s="7">
+        <v>32.549999999999997</v>
+      </c>
+      <c r="E120" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="F120" s="10">
+        <v>-2.75</v>
+      </c>
+      <c r="G120" s="10">
+        <v>-8.6199999999999992</v>
+      </c>
+      <c r="H120" s="9">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="I120" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J120" s="8">
+        <v>56.9</v>
+      </c>
+      <c r="K120" s="9">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="L120" s="8">
+        <v>56.9</v>
+      </c>
+      <c r="M120" s="9">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="N120" s="8">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O120" s="8">
+        <v>56.9</v>
+      </c>
+      <c r="P120" s="9">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="Q120" s="8">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>41244</v>
+      </c>
+      <c r="B121" s="7">
+        <v>31.75</v>
+      </c>
+      <c r="C121" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="D121" s="7">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="E121" s="7">
+        <v>30.05</v>
+      </c>
+      <c r="F121" s="10">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="G121" s="10">
+        <v>-3.33</v>
+      </c>
+      <c r="H121" s="9">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="I121" s="10">
+        <v>-2.5299999999999998</v>
+      </c>
+      <c r="J121" s="8">
+        <v>19.2</v>
+      </c>
+      <c r="K121" s="9">
+        <v>3.17</v>
+      </c>
+      <c r="L121" s="8">
+        <v>29</v>
+      </c>
+      <c r="M121" s="9">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="N121" s="10">
+        <v>-2.5299999999999998</v>
+      </c>
+      <c r="O121" s="8">
+        <v>19.2</v>
+      </c>
+      <c r="P121" s="9">
+        <v>3.17</v>
+      </c>
+      <c r="Q121" s="8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>41214</v>
+      </c>
+      <c r="B122" s="7">
+        <v>32</v>
+      </c>
+      <c r="C122" s="7">
+        <v>33</v>
+      </c>
+      <c r="D122" s="7">
+        <v>35.6</v>
+      </c>
+      <c r="E122" s="7">
+        <v>31.6</v>
+      </c>
+      <c r="F122" s="8">
+        <v>1</v>
+      </c>
+      <c r="G122" s="8">
+        <v>3.12</v>
+      </c>
+      <c r="H122" s="9">
+        <v>0</v>
+      </c>
+      <c r="I122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K122" s="9">
+        <v>0</v>
+      </c>
+      <c r="L122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M122" s="9">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="N122" s="10">
+        <v>-1.18</v>
+      </c>
+      <c r="O122" s="8">
+        <v>26</v>
+      </c>
+      <c r="P122" s="9">
+        <v>2.89</v>
+      </c>
+      <c r="Q122" s="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>41183</v>
+      </c>
+      <c r="B123" s="7">
+        <v>33</v>
+      </c>
+      <c r="C123" s="7">
+        <v>32</v>
+      </c>
+      <c r="D123" s="7">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="E123" s="7">
+        <v>31.15</v>
+      </c>
+      <c r="F123" s="10">
+        <v>-0.9</v>
+      </c>
+      <c r="G123" s="10">
+        <v>-2.74</v>
+      </c>
+      <c r="H123" s="9">
+        <v>0</v>
+      </c>
+      <c r="I123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K123" s="9">
+        <v>0</v>
+      </c>
+      <c r="L123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M123" s="9">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="N123" s="10">
+        <v>-1.92</v>
+      </c>
+      <c r="O123" s="8">
+        <v>26.4</v>
+      </c>
+      <c r="P123" s="9">
+        <v>2.61</v>
+      </c>
+      <c r="Q123" s="8">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>41153</v>
+      </c>
+      <c r="B124" s="7">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="C124" s="7">
+        <v>32.9</v>
+      </c>
+      <c r="D124" s="7">
+        <v>34.4</v>
+      </c>
+      <c r="E124" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="F124" s="10">
+        <v>-0.4</v>
+      </c>
+      <c r="G124" s="10">
+        <v>-1.2</v>
+      </c>
+      <c r="H124" s="9">
+        <v>0</v>
+      </c>
+      <c r="I124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K124" s="9">
+        <v>0</v>
+      </c>
+      <c r="L124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M124" s="9">
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="N124" s="10">
+        <v>-1.1200000000000001</v>
+      </c>
+      <c r="O124" s="8">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="P124" s="9">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="Q124" s="8">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
+        <v>41122</v>
+      </c>
+      <c r="B125" s="7">
+        <v>31.7</v>
+      </c>
+      <c r="C125" s="7">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="D125" s="7">
+        <v>35.4</v>
+      </c>
+      <c r="E125" s="7">
+        <v>30.4</v>
+      </c>
+      <c r="F125" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="G125" s="8">
+        <v>4.72</v>
+      </c>
+      <c r="H125" s="9">
+        <v>0</v>
+      </c>
+      <c r="I125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K125" s="9">
+        <v>0</v>
+      </c>
+      <c r="L125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M125" s="9">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="N125" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="O125" s="8">
+        <v>44.7</v>
+      </c>
+      <c r="P125" s="9">
+        <v>2.02</v>
+      </c>
+      <c r="Q125" s="8">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>41091</v>
+      </c>
+      <c r="B126" s="7">
+        <v>27.6</v>
+      </c>
+      <c r="C126" s="7">
+        <v>31.8</v>
+      </c>
+      <c r="D126" s="7">
+        <v>33.1</v>
+      </c>
+      <c r="E126" s="7">
+        <v>26.3</v>
+      </c>
+      <c r="F126" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="G126" s="8">
+        <v>15.85</v>
+      </c>
+      <c r="H126" s="9">
+        <v>0</v>
+      </c>
+      <c r="I126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K126" s="9">
+        <v>0</v>
+      </c>
+      <c r="L126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M126" s="9">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="N126" s="8">
+        <v>29.7</v>
+      </c>
+      <c r="O126" s="8">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="P126" s="9">
+        <v>1.72</v>
+      </c>
+      <c r="Q126" s="8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>41061</v>
+      </c>
+      <c r="B127" s="7">
+        <v>30.9</v>
+      </c>
+      <c r="C127" s="7">
+        <v>27.45</v>
+      </c>
+      <c r="D127" s="7">
+        <v>31.7</v>
+      </c>
+      <c r="E127" s="7">
+        <v>26.9</v>
+      </c>
+      <c r="F127" s="10">
+        <v>-2.65</v>
+      </c>
+      <c r="G127" s="10">
+        <v>-8.8000000000000007</v>
+      </c>
+      <c r="H127" s="9">
+        <v>0</v>
+      </c>
+      <c r="I127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K127" s="9">
+        <v>0</v>
+      </c>
+      <c r="L127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M127" s="9">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="N127" s="10">
+        <v>-11.5</v>
+      </c>
+      <c r="O127" s="8">
+        <v>12.6</v>
+      </c>
+      <c r="P127" s="9">
+        <v>1.43</v>
+      </c>
+      <c r="Q127" s="8">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
+        <v>41030</v>
+      </c>
+      <c r="B128" s="7">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="C128" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="D128" s="7">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="E128" s="7">
+        <v>29.4</v>
+      </c>
+      <c r="F128" s="10">
+        <v>-5.75</v>
+      </c>
+      <c r="G128" s="10">
+        <v>-16.04</v>
+      </c>
+      <c r="H128" s="9">
+        <v>0</v>
+      </c>
+      <c r="I128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K128" s="9">
+        <v>0</v>
+      </c>
+      <c r="L128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M128" s="9">
+        <v>0.255</v>
+      </c>
+      <c r="N128" s="10">
+        <v>-20.9</v>
+      </c>
+      <c r="O128" s="8">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="P128" s="9">
+        <v>1.26</v>
+      </c>
+      <c r="Q128" s="8">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A129" s="6">
+        <v>41000</v>
+      </c>
+      <c r="B129" s="7">
+        <v>41.9</v>
+      </c>
+      <c r="C129" s="7">
+        <v>35.85</v>
+      </c>
+      <c r="D129" s="7">
+        <v>42.3</v>
+      </c>
+      <c r="E129" s="7">
+        <v>32.75</v>
+      </c>
+      <c r="F129" s="10">
+        <v>-6.05</v>
+      </c>
+      <c r="G129" s="10">
+        <v>-14.44</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M129" s="9">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="N129" s="8">
+        <v>31.4</v>
+      </c>
+      <c r="O129" s="8">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="P129" s="9">
+        <v>1.01</v>
+      </c>
+      <c r="Q129" s="8">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
+        <v>40969</v>
+      </c>
+      <c r="B130" s="7">
+        <v>56</v>
+      </c>
+      <c r="C130" s="7">
+        <v>41.9</v>
+      </c>
+      <c r="D130" s="7">
+        <v>59</v>
+      </c>
+      <c r="E130" s="7">
+        <v>41.6</v>
+      </c>
+      <c r="F130" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="G130" s="8">
+        <v>4.75</v>
+      </c>
+      <c r="H130" s="9">
+        <v>0</v>
+      </c>
+      <c r="I130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K130" s="9">
+        <v>0</v>
+      </c>
+      <c r="L130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M130" s="9">
+        <v>0.245</v>
+      </c>
+      <c r="N130" s="10">
+        <v>-5.51</v>
+      </c>
+      <c r="O130" s="8">
+        <v>6.93</v>
+      </c>
+      <c r="P130" s="9">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="Q130" s="8">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A131" s="6">
+        <v>40940</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H131" s="9">
+        <v>0</v>
+      </c>
+      <c r="I131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K131" s="9">
+        <v>0</v>
+      </c>
+      <c r="L131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M131" s="9">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="N131" s="8">
+        <v>44.9</v>
+      </c>
+      <c r="O131" s="8">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="P131" s="9">
+        <v>0.438</v>
+      </c>
+      <c r="Q131" s="8">
+        <v>34.799999999999997</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
+        <v>40909</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H132" s="9">
+        <v>0</v>
+      </c>
+      <c r="I132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K132" s="9">
+        <v>0</v>
+      </c>
+      <c r="L132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M132" s="9">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="N132" s="10">
+        <v>-23.6</v>
+      </c>
+      <c r="O132" s="8">
+        <v>1.89</v>
+      </c>
+      <c r="P132" s="9">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="Q132" s="8">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
+        <v>40878</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H133" s="9">
+        <v>0</v>
+      </c>
+      <c r="I133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K133" s="9">
+        <v>0</v>
+      </c>
+      <c r="L133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M133" s="9">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="N133" s="8">
+        <v>7.6</v>
+      </c>
+      <c r="O133" s="8">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="P133" s="9">
+        <v>2.46</v>
+      </c>
+      <c r="Q133" s="8">
+        <v>73.900000000000006</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
+        <v>40848</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H134" s="9">
+        <v>0</v>
+      </c>
+      <c r="I134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K134" s="9">
+        <v>0</v>
+      </c>
+      <c r="L134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M134" s="9">
+        <v>0.218</v>
+      </c>
+      <c r="N134" s="10">
+        <v>-9.0299999999999994</v>
+      </c>
+      <c r="O134" s="8">
+        <v>31.8</v>
+      </c>
+      <c r="P134" s="9">
+        <v>2.23</v>
+      </c>
+      <c r="Q134" s="8">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
+        <v>40817</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H135" s="9">
+        <v>0</v>
+      </c>
+      <c r="I135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K135" s="9">
+        <v>0</v>
+      </c>
+      <c r="L135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M135" s="9">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="N135" s="8">
+        <v>10.6</v>
+      </c>
+      <c r="O135" s="8">
+        <v>23.8</v>
+      </c>
+      <c r="P135" s="9">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="Q135" s="8">
+        <v>86.4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
+        <v>40787</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H136" s="9">
+        <v>0</v>
+      </c>
+      <c r="I136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K136" s="9">
+        <v>0</v>
+      </c>
+      <c r="L136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M136" s="9">
+        <v>0.216</v>
+      </c>
+      <c r="N136" s="8">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="O136" s="8">
+        <v>56.8</v>
+      </c>
+      <c r="P136" s="9">
+        <v>1.77</v>
+      </c>
+      <c r="Q136" s="8">
+        <v>100.1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A137" s="6">
+        <v>40756</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H137" s="9">
+        <v>0</v>
+      </c>
+      <c r="I137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K137" s="9">
+        <v>0</v>
+      </c>
+      <c r="L137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M137" s="9">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N137" s="10">
+        <v>-0.46</v>
+      </c>
+      <c r="O137" s="8">
+        <v>2.36</v>
+      </c>
+      <c r="P137" s="9">
+        <v>1.55</v>
+      </c>
+      <c r="Q137" s="8">
+        <v>108.2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
+        <v>40725</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H138" s="9">
+        <v>0</v>
+      </c>
+      <c r="I138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K138" s="9">
+        <v>0</v>
+      </c>
+      <c r="L138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M138" s="9">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="N138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O138" s="8">
+        <v>12.6</v>
+      </c>
+      <c r="P138" s="9">
+        <v>1.35</v>
+      </c>
+      <c r="Q138" s="8">
+        <v>147.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A139" s="6">
+        <v>40695</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H139" s="9">
+        <v>0</v>
+      </c>
+      <c r="I139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K139" s="9">
+        <v>0</v>
+      </c>
+      <c r="L139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q139" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
+        <v>40664</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H140" s="9">
+        <v>0</v>
+      </c>
+      <c r="I140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K140" s="9">
+        <v>0</v>
+      </c>
+      <c r="L140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q140" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A141" s="6">
+        <v>40634</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H141" s="9">
+        <v>0</v>
+      </c>
+      <c r="I141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K141" s="9">
+        <v>0</v>
+      </c>
+      <c r="L141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q141" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A142" s="6">
+        <v>40603</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H142" s="9">
+        <v>0</v>
+      </c>
+      <c r="I142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K142" s="9">
+        <v>0</v>
+      </c>
+      <c r="L142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q142" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A143" s="6">
+        <v>40575</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H143" s="9">
+        <v>0</v>
+      </c>
+      <c r="I143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K143" s="9">
+        <v>0</v>
+      </c>
+      <c r="L143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q143" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A144" s="6">
+        <v>40544</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H144" s="9">
+        <v>0</v>
+      </c>
+      <c r="I144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K144" s="9">
+        <v>0</v>
+      </c>
+      <c r="L144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q144" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4518,7 +8822,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>